--- a/Voedselweb_InvulTabel.xlsx
+++ b/Voedselweb_InvulTabel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aliciahamer/Library/CloudStorage/OneDrive-WageningenUniversity&amp;Research/TOP-projecten/WP3 - Draagkracht/3_Data/1_VoedselWeb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A849667-138F-9A4D-A3A1-6FC8C5E36186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6C3234-E854-CF42-AE9B-4B41D490C131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16820" xr2:uid="{7A466837-12FA-7643-B683-5B6BE25E44C1}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>id</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Gemiddelde waarde</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -469,12 +472,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F1231E-7DEF-314E-BBA7-023CF8AB8600}">
-  <dimension ref="D1"/>
+  <dimension ref="D1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="4:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D1" t="s">
         <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Voedselweb_InvulTabel.xlsx
+++ b/Voedselweb_InvulTabel.xlsx
@@ -8,15 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aliciahamer/Library/CloudStorage/OneDrive-WageningenUniversity&amp;Research/TOP-projecten/WP3 - Draagkracht/3_Data/1_VoedselWeb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6C3234-E854-CF42-AE9B-4B41D490C131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64537C10-DD35-BC4E-A184-4CD66811776C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16820" xr2:uid="{7A466837-12FA-7643-B683-5B6BE25E44C1}"/>
+    <workbookView xWindow="680" yWindow="760" windowWidth="28040" windowHeight="16820" activeTab="1" xr2:uid="{7A466837-12FA-7643-B683-5B6BE25E44C1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mooi_Nodes" sheetId="2" r:id="rId1"/>
-    <sheet name="R_Nodes" sheetId="1" r:id="rId2"/>
-    <sheet name="Mooi_Edges" sheetId="3" r:id="rId3"/>
-    <sheet name="R_Edges" sheetId="4" r:id="rId4"/>
+    <sheet name="R_Nodes" sheetId="1" r:id="rId1"/>
+    <sheet name="R_Edges" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
@@ -38,26 +36,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={0DDA50C9-EF3D-1549-9C5E-3CA96B3B0DAA}</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{0DDA50C9-EF3D-1549-9C5E-3CA96B3B0DAA}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Ruwe Schatting, dit bepaald de grootte van je Node automatisch</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="80">
   <si>
     <t>id</t>
   </si>
@@ -77,17 +57,235 @@
     <t>font.size</t>
   </si>
   <si>
-    <t>Gemiddelde waarde</t>
-  </si>
-  <si>
-    <t>test</t>
+    <t>sun</t>
+  </si>
+  <si>
+    <t>fyto</t>
+  </si>
+  <si>
+    <t>microfyto</t>
+  </si>
+  <si>
+    <t>macrofyt</t>
+  </si>
+  <si>
+    <t>detritus</t>
+  </si>
+  <si>
+    <t>zoopl</t>
+  </si>
+  <si>
+    <t>schelp</t>
+  </si>
+  <si>
+    <t>macrofauna</t>
+  </si>
+  <si>
+    <t>krab</t>
+  </si>
+  <si>
+    <t>vis</t>
+  </si>
+  <si>
+    <t>zeezoog</t>
+  </si>
+  <si>
+    <t>herbvogel</t>
+  </si>
+  <si>
+    <t>benthvogel</t>
+  </si>
+  <si>
+    <t>visvogel</t>
+  </si>
+  <si>
+    <t>Zon</t>
+  </si>
+  <si>
+    <t>Fytoplankton</t>
+  </si>
+  <si>
+    <t>Microfytobenthos</t>
+  </si>
+  <si>
+    <t>Macrofyten</t>
+  </si>
+  <si>
+    <t>Detritus</t>
+  </si>
+  <si>
+    <t>Zooplankton</t>
+  </si>
+  <si>
+    <t>Filtreerende Schelpdieren</t>
+  </si>
+  <si>
+    <t>Deposit feeders</t>
+  </si>
+  <si>
+    <t>Krabben/Zeesterren</t>
+  </si>
+  <si>
+    <t>Vis</t>
+  </si>
+  <si>
+    <t>Zeezoogdieren</t>
+  </si>
+  <si>
+    <t>Herbivore vogels</t>
+  </si>
+  <si>
+    <t>Benthivore vogels</t>
+  </si>
+  <si>
+    <t>Visetende vogels</t>
+  </si>
+  <si>
+    <t>producent</t>
+  </si>
+  <si>
+    <t>primair</t>
+  </si>
+  <si>
+    <t>secundair</t>
+  </si>
+  <si>
+    <t>top</t>
+  </si>
+  <si>
+    <t>Primaire productie: fytoplankton              &lt;br&gt; ~ 1.0 g/m2 (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Primaire productie: microfytobenthos          &lt;br&gt; ~ 1.7 g/m2 (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Macrofyten (zeegras/kwelderplanten)</t>
+  </si>
+  <si>
+    <t>Detritus / organisch materiaal                &lt;br&gt; ~ 1.9 g/m2  (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Kokkels, mosselen, oesters                    &lt;br&gt; ~ 13.8 g/m2 (Smaal &amp; Nienhuis 1992, exl. oesters)              &lt;br&gt; ~ 11.5 g/m2 (Smaal et al. 2013)                                                   &lt;br&gt;   WOT gemiddelde 2020-2026</t>
+  </si>
+  <si>
+    <t>Zoöplankton                                                &lt;br&gt; ~ 0.5 g/m2  (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Bodemfauna / deposit feeders                  &lt;br&gt; ~ 2.2 g/m2  (Smaal &amp; Nienhuis 1992) &lt;br&gt;   MWTL gemiddelde 2020-2026</t>
+  </si>
+  <si>
+    <t>Krabben en Zeesterren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vis                                           &lt;br&gt;   DFS gemiddelde 2020-2026 </t>
+  </si>
+  <si>
+    <t>Herbivore vogels (grazen op macrofyten)</t>
+  </si>
+  <si>
+    <t>Benthivore vogels (eten bodemdieren)</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>Zeezoogdieren (bv. zeehond)</t>
+  </si>
+  <si>
+    <t>box</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>from</t>
+  </si>
+  <si>
+    <t>to</t>
+  </si>
+  <si>
+    <t>width</t>
+  </si>
+  <si>
+    <t>arrows</t>
+  </si>
+  <si>
+    <t>PP Microfytobenthos             &lt;br&gt; 1992?: ~100-200 g/m2/yr (Smaal 1992)
+                                     &lt;br&gt; 1994?: ~150-242 g/m2/yr (de Jong 1994)</t>
+  </si>
+  <si>
+    <t>PP Macrofyten                   &lt;br&gt; ??</t>
+  </si>
+  <si>
+    <t>Detritus ‚Üí Filtreerders           &lt;br&gt; 50-100 g/m2/yr (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Detritus ‚Üí Microfytobenthos       &lt;br&gt; &lt; 25 g/m2/yr (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Fytoplankton ‚Üí Zo√∂plankton        &lt;br&gt; &lt; 25 g/m2/yr (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Fytoplankton ‚Üí Filtreerders       &lt;br&gt; 25-50 g/m2/yr (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Microfytobenthos ‚Üí Detritus       &lt;br&gt; &lt; 25 g/m2/yr (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Microfytobenthos ‚Üí Depositfeeder  &lt;br&gt; &lt; 25 g/m2/yr (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Macrofyten ‚Üí Herbivore vogels</t>
+  </si>
+  <si>
+    <t>Zo√∂plankton ‚Üí Vis</t>
+  </si>
+  <si>
+    <t>Filtreerders ‚Üí Krabben</t>
+  </si>
+  <si>
+    <t>Filtreerders ‚Üí Vis</t>
+  </si>
+  <si>
+    <t>Filtreerders ‚Üí Benthivore vogels</t>
+  </si>
+  <si>
+    <t>Filtreerders ‚Üí Detritus           &lt;br&gt; 50-100 g/m2/yr (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Depositfeeder ‚Üí Vis</t>
+  </si>
+  <si>
+    <t>Krabben ‚Üí Vis</t>
+  </si>
+  <si>
+    <t>Krabben ‚Üí Benthivore vogels</t>
+  </si>
+  <si>
+    <t>Vis ‚Üí Zeezoogdieren</t>
+  </si>
+  <si>
+    <t>PP Fytoplankton                 &lt;br&gt; 1995: ~300 g/m2/yr (Smaal et al. 2013)
+                                               &lt;br&gt; 2020: ~200 g/m2/yr (Dijkman et al. 2026)</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>Detritus -&gt; Depositfeeder          &lt;br&gt; &lt; 25 g/m2/yr (Smaal &amp; Nienhuis 1992)</t>
+  </si>
+  <si>
+    <t>Vis -&gt; Visetende vogels</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -96,10 +294,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow (Body)"/>
     </font>
   </fonts>
   <fills count="2">
@@ -110,7 +314,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -118,12 +322,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -142,9 +365,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Hamer, Alicia" id="{61AAE24C-77C7-6441-9ABE-8546B70181F6}" userId="S::alicia.hamer@wur.nl::526dc1b0-728f-42ab-8928-af2e2cdad6b6" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -462,80 +683,857 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D1" dT="2026-10-06T17:26:07.69" personId="{61AAE24C-77C7-6441-9ABE-8546B70181F6}" id="{0DDA50C9-EF3D-1549-9C5E-3CA96B3B0DAA}">
-    <text>Ruwe Schatting, dit bepaald de grootte van je Node automatisch</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F1231E-7DEF-314E-BBA7-023CF8AB8600}">
-  <dimension ref="D1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906EFAF7-4849-0A4C-9DAA-E241F6F6A7C3}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="4" max="4" width="65.1640625" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="F5">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>18</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13">
+        <v>120</v>
+      </c>
+      <c r="F13">
+        <v>18</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+      <c r="H13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14">
+        <v>120</v>
+      </c>
+      <c r="F14">
+        <v>18</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15">
+        <v>120</v>
+      </c>
+      <c r="F15">
+        <v>18</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002F4FA5-6460-4E49-8AAA-6C2311F8B261}">
-  <dimension ref="A1"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E420CA47-F803-5D49-B4AC-CC88B0C8AD29}">
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E420CA47-F803-5D49-B4AC-CC88B0C8AD29}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="66" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="6">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>